--- a/AAAGameData/DataTables/CharacterMAFactoryTable.xlsx
+++ b/AAAGameData/DataTables/CharacterMAFactoryTable.xlsx
@@ -62,10 +62,10 @@
     <t>Archer</t>
   </si>
   <si>
-    <t>Assets/AAAGame/SOs/MoveCompFactory/NoMoveFactory.asset</t>
-  </si>
-  <si>
-    <t>Assets/AAAGame/SOs/AttackCompFactory/NoAtkFactory.asset</t>
+    <t>NoMoveFactory</t>
+  </si>
+  <si>
+    <t>NoAtkFactory</t>
   </si>
   <si>
     <t>Shield</t>
